--- a/sheets/대금율보/검수/가브리엘 오보에.xlsx
+++ b/sheets/대금율보/검수/가브리엘 오보에.xlsx
@@ -3553,21 +3553,13 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="24"/>
       <c r="E5" s="25"/>
       <c r="F5" s="21"/>
       <c r="G5" s="23"/>
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="24"/>
       <c r="K5" s="25"/>
       <c r="L5" s="21"/>
       <c r="M5" s="23"/>
@@ -3587,14 +3579,14 @@
       <c r="E6" s="26"/>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="G6" s="27"/>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3608,14 +3600,14 @@
       <c r="K6" s="26"/>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="M6" s="27"/>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3672,7 +3664,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -3681,7 +3673,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㳞</t>
         </is>
       </c>
@@ -3697,7 +3689,7 @@
       <c r="K8" s="23"/>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㳞</t>
         </is>
       </c>
@@ -3759,14 +3751,14 @@
       <c r="C10" s="26"/>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢ʒ</t>
         </is>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3779,14 +3771,14 @@
       <c r="I10" s="26"/>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢ʒ</t>
         </is>
       </c>
       <c r="K10" s="27"/>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3851,7 +3843,7 @@
       <c r="G12" s="23"/>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3866,7 +3858,7 @@
       <c r="M12" s="23"/>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3940,7 +3932,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4012,14 +4004,14 @@
       <c r="E17" s="23"/>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="G17" s="25"/>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4028,14 +4020,14 @@
       <c r="K17" s="23"/>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="M17" s="25"/>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/가브리엘 오보에.xlsx
+++ b/sheets/대금율보/검수/가브리엘 오보에.xlsx
@@ -3425,26 +3425,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -3566,7 +3566,7 @@
       <c r="N5" s="21"/>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="26"/>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="O6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       <c r="N11" s="21"/>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="O12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="O14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="24" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       <c r="N16" s="21"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4088,6 +4088,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>